--- a/artfynd/A 17004-2024 artfynd.xlsx
+++ b/artfynd/A 17004-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81863456</v>
+        <v>75761443</v>
       </c>
       <c r="B2" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>174</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ekeby kyrka, 5,2 km O-ut, Upl</t>
+          <t>Ekeby kyrka, 4,8 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>684519.0037925472</v>
+        <v>684067</v>
       </c>
       <c r="R2" t="n">
-        <v>6665456.992534428</v>
+        <v>6665907</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,27 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-09-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-09-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sly.</t>
+          <t>2018-07-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +792,7 @@
         <v>81863459</v>
       </c>
       <c r="B3" t="n">
-        <v>103346</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>684519.0037925472</v>
+        <v>684519</v>
       </c>
       <c r="R3" t="n">
-        <v>6665456.992534428</v>
+        <v>6665457</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,19 +860,9 @@
           <t>2019-09-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,12 +897,7 @@
         <v>81863458</v>
       </c>
       <c r="B4" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -964,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>684519.0037925472</v>
+        <v>684519</v>
       </c>
       <c r="R4" t="n">
-        <v>6665456.992534428</v>
+        <v>6665457</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,19 +965,9 @@
           <t>2019-09-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,6 +992,222 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>81863464</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ekeby kyrka, 5,3 km O-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>684615</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6665454</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ekeby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-09-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-09-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>81863456</v>
+      </c>
+      <c r="B6" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ekeby kyrka, 5,2 km O-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>684519</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6665457</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ekeby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-09-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-09-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sly.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>

--- a/artfynd/A 17004-2024 artfynd.xlsx
+++ b/artfynd/A 17004-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75761443</t>
         </is>
       </c>
     </row>
@@ -891,6 +901,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81863459</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81863458</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81863464</t>
         </is>
       </c>
     </row>
@@ -1212,8 +1237,20 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81863456</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>